--- a/survey_templates/024_genetic_feedback_loop_research_data_collection_form--survey_templates.xlsx
+++ b/survey_templates/024_genetic_feedback_loop_research_data_collection_form--survey_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -742,8 +742,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -771,12 +771,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'participant_type',_'label':_'participant_type',_'value':_'participant'}</t>
+          <t>participant_type</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Participant Type', 'label': 'Participant Type', 'value': 'Participant'}</t>
+          <t>Participant Type</t>
         </is>
       </c>
     </row>
@@ -788,12 +788,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'control',_'label':_'control'}</t>
+          <t>control</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Control', 'label': 'Control'}</t>
+          <t>Control</t>
         </is>
       </c>
     </row>
@@ -805,12 +805,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'donor',_'label':_'donor'}</t>
+          <t>donor</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Donor', 'label': 'Donor'}</t>
+          <t>Donor</t>
         </is>
       </c>
     </row>
@@ -822,12 +822,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'participant_age',_'label':_'participant_age',_'value':_'participant_age'}</t>
+          <t>participant_age</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'participant_age', 'label': 'participant_age', 'value': 'participant_age'}</t>
+          <t>participant age</t>
         </is>
       </c>
     </row>
@@ -839,12 +839,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_5,_'name':_'study_group',_'label':_'study_group',_'value':_'study_group'}</t>
+          <t>study_group</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 5, 'name': 'study_group', 'label': 'study_group', 'value': 'study_group'}</t>
+          <t>study group</t>
         </is>
       </c>
     </row>
@@ -856,12 +856,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_6,_'name':_'gender',_'label':_'gender',_'value':_'gender'}</t>
+          <t>gender</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 6, 'name': 'gender', 'label': 'gender', 'value': 'gender'}</t>
+          <t>gender</t>
         </is>
       </c>
     </row>
@@ -873,12 +873,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_7,_'name':_'relationship_1',_'label':_'',_'value':_''}</t>
+          <t>relationship_1</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 7, 'name': 'relationship_1', 'label': '', 'value': ''}</t>
+          <t>relationship 1</t>
         </is>
       </c>
     </row>
@@ -890,12 +890,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_8,_'name':_'relationship_2',_'label':_'',_'value':_''}</t>
+          <t>relationship_2</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 8, 'name': 'relationship_2', 'label': '', 'value': ''}</t>
+          <t>relationship 2</t>
         </is>
       </c>
     </row>
@@ -907,12 +907,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_9,_'name':_'relationship_3',_'label':_'',_'value':_''}</t>
+          <t>relationship_3</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 9, 'name': 'relationship_3', 'label': '', 'value': ''}</t>
+          <t>relationship 3</t>
         </is>
       </c>
     </row>
@@ -924,12 +924,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_10,_'name':_'genetic_info_1',_'label':_'',_'value':_''}</t>
+          <t>genetic_info_1</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 10, 'name': 'genetic_info_1', 'label': '', 'value': ''}</t>
+          <t>genetic info 1</t>
         </is>
       </c>
     </row>
@@ -941,12 +941,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_11,_'name':_'genetic_info_2',_'label':_'',_'value':_''}</t>
+          <t>genetic_info_2</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 11, 'name': 'genetic_info_2', 'label': '', 'value': ''}</t>
+          <t>genetic info 2</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_12,_'name':_'genetic_option_1',_'label':_'',_'value':_''}</t>
+          <t>genetic_option_1</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 12, 'name': 'genetic_option_1', 'label': '', 'value': ''}</t>
+          <t>genetic option 1</t>
         </is>
       </c>
     </row>
@@ -975,12 +975,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_13,_'name':_'genetic_option_2',_'label':_'',_'value':_''}</t>
+          <t>genetic_option_2</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 13, 'name': 'genetic_option_2', 'label': '', 'value': ''}</t>
+          <t>genetic option 2</t>
         </is>
       </c>
     </row>
